--- a/output/lda_results_full_dataset_topic_num_5.xlsx
+++ b/output/lda_results_full_dataset_topic_num_5.xlsx
@@ -5428,7 +5428,7 @@
         <v>0.6262999773025513</v>
       </c>
       <c r="H7">
-        <v>0.3671999871730804</v>
+        <v>0.3673000037670135</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -5897,10 +5897,10 @@
         <v>1</v>
       </c>
       <c r="G30">
-        <v>0.6262000203132629</v>
+        <v>0.6259999871253967</v>
       </c>
       <c r="I30">
-        <v>0.3659999966621399</v>
+        <v>0.3662000000476837</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -5920,7 +5920,7 @@
         <v>3</v>
       </c>
       <c r="F31">
-        <v>0.4181999862194061</v>
+        <v>0.4180999994277954</v>
       </c>
       <c r="I31">
         <v>0.5759999752044678</v>
@@ -6092,10 +6092,10 @@
         <v>1</v>
       </c>
       <c r="G39">
-        <v>0.6139000058174133</v>
+        <v>0.6140999794006348</v>
       </c>
       <c r="I39">
-        <v>0.3810000121593475</v>
+        <v>0.3808000087738037</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -6633,7 +6633,7 @@
         <v>0.3813999891281128</v>
       </c>
       <c r="J65">
-        <v>0.6098999977111816</v>
+        <v>0.6097999811172485</v>
       </c>
     </row>
     <row r="66" spans="1:10">
@@ -6656,7 +6656,7 @@
         <v>0.6626999974250793</v>
       </c>
       <c r="I66">
-        <v>0.3276000022888184</v>
+        <v>0.3274999856948853</v>
       </c>
     </row>
     <row r="67" spans="1:10">
@@ -6696,7 +6696,7 @@
         <v>2</v>
       </c>
       <c r="H68">
-        <v>0.6119999885559082</v>
+        <v>0.6121000051498413</v>
       </c>
       <c r="J68">
         <v>0.3824000060558319</v>
@@ -6877,7 +6877,7 @@
         <v>0.4417999982833862</v>
       </c>
       <c r="I76">
-        <v>0.459199994802475</v>
+        <v>0.4593000113964081</v>
       </c>
     </row>
     <row r="77" spans="1:10">
@@ -6980,10 +6980,10 @@
         <v>0</v>
       </c>
       <c r="F81">
-        <v>0.7167999744415283</v>
+        <v>0.7161999940872192</v>
       </c>
       <c r="H81">
-        <v>0.2617999911308289</v>
+        <v>0.2624000012874603</v>
       </c>
     </row>
     <row r="82" spans="1:10">
@@ -7003,10 +7003,10 @@
         <v>3</v>
       </c>
       <c r="H82">
-        <v>0.2596000134944916</v>
+        <v>0.2594999969005585</v>
       </c>
       <c r="I82">
-        <v>0.4959000051021576</v>
+        <v>0.4959999918937683</v>
       </c>
       <c r="J82">
         <v>0.2409999966621399</v>
@@ -7069,10 +7069,10 @@
         <v>0</v>
       </c>
       <c r="F85">
-        <v>0.5684000253677368</v>
+        <v>0.5683000087738037</v>
       </c>
       <c r="I85">
-        <v>0.4194999933242798</v>
+        <v>0.4196000099182129</v>
       </c>
     </row>
     <row r="86" spans="1:10">
@@ -7173,7 +7173,7 @@
         <v>0.626800000667572</v>
       </c>
       <c r="I89">
-        <v>0.3603000044822693</v>
+        <v>0.36039999127388</v>
       </c>
     </row>
     <row r="90" spans="1:10">
@@ -7302,7 +7302,7 @@
         <v>1</v>
       </c>
       <c r="G95">
-        <v>0.5759999752044678</v>
+        <v>0.5759000182151794</v>
       </c>
       <c r="I95">
         <v>0.416700005531311</v>
@@ -7385,7 +7385,7 @@
         <v>1</v>
       </c>
       <c r="G99">
-        <v>0.5072000026702881</v>
+        <v>0.5073000192642212</v>
       </c>
       <c r="H99">
         <v>0.4894999861717224</v>
@@ -7474,7 +7474,7 @@
         <v>0.4363000094890594</v>
       </c>
       <c r="J103">
-        <v>0.555899977684021</v>
+        <v>0.5559999942779541</v>
       </c>
     </row>
     <row r="104" spans="1:10">
@@ -7520,7 +7520,7 @@
         <v>0.01099999994039536</v>
       </c>
       <c r="H105">
-        <v>0.4887000024318695</v>
+        <v>0.4885999858379364</v>
       </c>
       <c r="I105">
         <v>0.01190000027418137</v>
@@ -7586,10 +7586,10 @@
         <v>0</v>
       </c>
       <c r="F108">
-        <v>0.7258999943733215</v>
+        <v>0.7250999808311462</v>
       </c>
       <c r="G108">
-        <v>0.2603000104427338</v>
+        <v>0.2610999941825867</v>
       </c>
     </row>
     <row r="109" spans="1:10">
@@ -7735,7 +7735,7 @@
         <v>1</v>
       </c>
       <c r="F115">
-        <v>0.4587999880313873</v>
+        <v>0.4589000046253204</v>
       </c>
       <c r="G115">
         <v>0.5235999822616577</v>
@@ -7781,10 +7781,10 @@
         <v>2</v>
       </c>
       <c r="F117">
-        <v>0.4668000042438507</v>
+        <v>0.4666999876499176</v>
       </c>
       <c r="H117">
-        <v>0.5210999846458435</v>
+        <v>0.5212000012397766</v>
       </c>
     </row>
     <row r="118" spans="1:10">
@@ -7887,10 +7887,10 @@
         <v>0</v>
       </c>
       <c r="F122">
-        <v>0.5600000023841858</v>
+        <v>0.5601000189781189</v>
       </c>
       <c r="I122">
-        <v>0.4266000092029572</v>
+        <v>0.426499992609024</v>
       </c>
     </row>
     <row r="123" spans="1:10">
@@ -8028,10 +8028,10 @@
         <v>2</v>
       </c>
       <c r="G128">
-        <v>0.3061999976634979</v>
+        <v>0.3061000108718872</v>
       </c>
       <c r="H128">
-        <v>0.6741999983787537</v>
+        <v>0.6743000149726868</v>
       </c>
     </row>
     <row r="129" spans="1:10">
@@ -8175,7 +8175,7 @@
         <v>0.4318000078201294</v>
       </c>
       <c r="H134">
-        <v>0.5630999803543091</v>
+        <v>0.5631999969482422</v>
       </c>
     </row>
     <row r="135" spans="1:10">
@@ -8396,7 +8396,7 @@
         <v>0.4652999937534332</v>
       </c>
       <c r="I144">
-        <v>0.3427999913692474</v>
+        <v>0.3427000045776367</v>
       </c>
       <c r="J144">
         <v>0.1894000023603439</v>
@@ -8462,7 +8462,7 @@
         <v>2</v>
       </c>
       <c r="H147">
-        <v>0.5634999871253967</v>
+        <v>0.5633999705314636</v>
       </c>
       <c r="J147">
         <v>0.4282000064849854</v>
@@ -8628,7 +8628,7 @@
         <v>0</v>
       </c>
       <c r="F155">
-        <v>0.5540000200271606</v>
+        <v>0.5539000034332275</v>
       </c>
       <c r="H155">
         <v>0.296999990940094</v>
@@ -8674,10 +8674,10 @@
         <v>1</v>
       </c>
       <c r="G157">
-        <v>0.582099974155426</v>
+        <v>0.5821999907493591</v>
       </c>
       <c r="H157">
-        <v>0.4047000110149384</v>
+        <v>0.4045999944210052</v>
       </c>
     </row>
     <row r="158" spans="1:10">
@@ -8697,13 +8697,13 @@
         <v>1</v>
       </c>
       <c r="G158">
-        <v>0.4891999959945679</v>
+        <v>0.489300012588501</v>
       </c>
       <c r="H158">
         <v>0.1754000037908554</v>
       </c>
       <c r="J158">
-        <v>0.3319999873638153</v>
+        <v>0.3318000137805939</v>
       </c>
     </row>
     <row r="159" spans="1:10">
@@ -8966,10 +8966,10 @@
         <v>4</v>
       </c>
       <c r="F171">
-        <v>0.2312999963760376</v>
+        <v>0.2313999980688095</v>
       </c>
       <c r="H171">
-        <v>0.3158000111579895</v>
+        <v>0.3156999945640564</v>
       </c>
       <c r="J171">
         <v>0.449400007724762</v>
@@ -9012,10 +9012,10 @@
         <v>2</v>
       </c>
       <c r="H173">
-        <v>0.5511000156402588</v>
+        <v>0.5509999990463257</v>
       </c>
       <c r="J173">
-        <v>0.4372999966144562</v>
+        <v>0.4374000132083893</v>
       </c>
     </row>
     <row r="174" spans="1:10">
@@ -9193,7 +9193,7 @@
         <v>0.4666999876499176</v>
       </c>
       <c r="G181">
-        <v>0.3445000052452087</v>
+        <v>0.3445999920368195</v>
       </c>
       <c r="J181">
         <v>0.1854999959468842</v>
@@ -9216,10 +9216,10 @@
         <v>0</v>
       </c>
       <c r="F182">
-        <v>0.7379999756813049</v>
+        <v>0.7379000186920166</v>
       </c>
       <c r="I182">
-        <v>0.2486000061035156</v>
+        <v>0.2486999928951263</v>
       </c>
     </row>
     <row r="183" spans="1:10">
@@ -9285,7 +9285,7 @@
         <v>0.3657000064849854</v>
       </c>
       <c r="I185">
-        <v>0.6191999912261963</v>
+        <v>0.6193000078201294</v>
       </c>
     </row>
     <row r="186" spans="1:10">
@@ -9420,7 +9420,7 @@
         <v>0</v>
       </c>
       <c r="F191">
-        <v>0.8439000248908997</v>
+        <v>0.843999981880188</v>
       </c>
       <c r="H191">
         <v>0.1468999981880188</v>
@@ -9506,10 +9506,10 @@
         <v>0</v>
       </c>
       <c r="F195">
-        <v>0.5942999720573425</v>
+        <v>0.5945000052452087</v>
       </c>
       <c r="J195">
-        <v>0.4004000127315521</v>
+        <v>0.4002000093460083</v>
       </c>
     </row>
     <row r="196" spans="1:10">
@@ -9681,7 +9681,7 @@
         <v>0.5551000237464905</v>
       </c>
       <c r="J203">
-        <v>0.4397999942302704</v>
+        <v>0.4397000074386597</v>
       </c>
     </row>
     <row r="204" spans="1:10">
@@ -9859,10 +9859,10 @@
         <v>3</v>
       </c>
       <c r="F211">
-        <v>0.1516000032424927</v>
+        <v>0.1515000015497208</v>
       </c>
       <c r="I211">
-        <v>0.8391000032424927</v>
+        <v>0.8392000198364258</v>
       </c>
     </row>
     <row r="212" spans="1:10">
@@ -9882,10 +9882,10 @@
         <v>3</v>
       </c>
       <c r="I212">
-        <v>0.6833000183105469</v>
+        <v>0.6833999752998352</v>
       </c>
       <c r="J212">
-        <v>0.3039000034332275</v>
+        <v>0.3037999868392944</v>
       </c>
     </row>
     <row r="213" spans="1:10">
@@ -9925,10 +9925,10 @@
         <v>3</v>
       </c>
       <c r="H214">
-        <v>0.2407999932765961</v>
+        <v>0.240899994969368</v>
       </c>
       <c r="I214">
-        <v>0.7494999766349792</v>
+        <v>0.7494000196456909</v>
       </c>
     </row>
     <row r="215" spans="1:10">
@@ -9948,13 +9948,13 @@
         <v>1</v>
       </c>
       <c r="G215">
-        <v>0.425900012254715</v>
+        <v>0.4257999956607819</v>
       </c>
       <c r="H215">
         <v>0.2739999890327454</v>
       </c>
       <c r="J215">
-        <v>0.2973999977111816</v>
+        <v>0.2975000143051147</v>
       </c>
     </row>
     <row r="216" spans="1:10">
@@ -10364,10 +10364,10 @@
         <v>0</v>
       </c>
       <c r="F234">
-        <v>0.5823000073432922</v>
+        <v>0.5824000239372253</v>
       </c>
       <c r="H234">
-        <v>0.3962999880313873</v>
+        <v>0.3962000012397766</v>
       </c>
     </row>
     <row r="235" spans="1:10">
@@ -10654,7 +10654,7 @@
         <v>0.5246999859809875</v>
       </c>
       <c r="H247">
-        <v>0.4598999917507172</v>
+        <v>0.4598000049591064</v>
       </c>
     </row>
     <row r="248" spans="1:10">
@@ -10674,10 +10674,10 @@
         <v>1</v>
       </c>
       <c r="F248">
-        <v>0.2196000069379807</v>
+        <v>0.2194000035524368</v>
       </c>
       <c r="G248">
-        <v>0.76910001039505</v>
+        <v>0.7692999839782715</v>
       </c>
     </row>
     <row r="249" spans="1:10">
@@ -10757,10 +10757,10 @@
         <v>2</v>
       </c>
       <c r="H252">
-        <v>0.5</v>
+        <v>0.4997000098228455</v>
       </c>
       <c r="J252">
-        <v>0.4916000068187714</v>
+        <v>0.4918999969959259</v>
       </c>
     </row>
     <row r="253" spans="1:10">
@@ -11072,10 +11072,10 @@
         <v>3</v>
       </c>
       <c r="F267">
-        <v>0.3170000016689301</v>
+        <v>0.3169000148773193</v>
       </c>
       <c r="I267">
-        <v>0.667900025844574</v>
+        <v>0.6679999828338623</v>
       </c>
     </row>
     <row r="268" spans="1:10">
@@ -11095,10 +11095,10 @@
         <v>0</v>
       </c>
       <c r="F268">
-        <v>0.5449000000953674</v>
+        <v>0.5450000166893005</v>
       </c>
       <c r="G268">
-        <v>0.4426999986171722</v>
+        <v>0.4426000118255615</v>
       </c>
     </row>
     <row r="269" spans="1:10">
@@ -11207,7 +11207,7 @@
         <v>0.3583000004291534</v>
       </c>
       <c r="H273">
-        <v>0.6394000053405762</v>
+        <v>0.6392999887466431</v>
       </c>
     </row>
     <row r="274" spans="1:10">
@@ -11560,7 +11560,7 @@
         <v>0</v>
       </c>
       <c r="F289">
-        <v>0.8391000032424927</v>
+        <v>0.8392000198364258</v>
       </c>
       <c r="J289">
         <v>0.1498000025749207</v>
@@ -11738,7 +11738,7 @@
         <v>0.6468999981880188</v>
       </c>
       <c r="J297">
-        <v>0.3474999964237213</v>
+        <v>0.3476000130176544</v>
       </c>
     </row>
     <row r="298" spans="1:10">
@@ -11821,7 +11821,7 @@
         <v>1</v>
       </c>
       <c r="G301">
-        <v>0.5902000069618225</v>
+        <v>0.5903000235557556</v>
       </c>
       <c r="H301">
         <v>0.4040000140666962</v>
@@ -11867,7 +11867,7 @@
         <v>0.4923000037670135</v>
       </c>
       <c r="J303">
-        <v>0.5008000135421753</v>
+        <v>0.5008999705314636</v>
       </c>
     </row>
     <row r="304" spans="1:10">
@@ -12128,7 +12128,7 @@
         <v>0.4156000018119812</v>
       </c>
       <c r="I315">
-        <v>0.5803999900817871</v>
+        <v>0.580299973487854</v>
       </c>
     </row>
     <row r="316" spans="1:10">
@@ -12171,7 +12171,7 @@
         <v>0.8285999894142151</v>
       </c>
       <c r="J317">
-        <v>0.164900004863739</v>
+        <v>0.1648000031709671</v>
       </c>
     </row>
     <row r="318" spans="1:10">
@@ -12214,10 +12214,10 @@
         <v>4</v>
       </c>
       <c r="G319">
-        <v>0.478300005197525</v>
+        <v>0.4785999953746796</v>
       </c>
       <c r="J319">
-        <v>0.5054000020027161</v>
+        <v>0.5051000118255615</v>
       </c>
     </row>
     <row r="320" spans="1:10">
@@ -12532,7 +12532,7 @@
         <v>0.6938999891281128</v>
       </c>
       <c r="H334">
-        <v>0.3037000000476837</v>
+        <v>0.3037999868392944</v>
       </c>
     </row>
     <row r="335" spans="1:10">
@@ -12718,7 +12718,7 @@
         <v>2</v>
       </c>
       <c r="G343">
-        <v>0.4596000015735626</v>
+        <v>0.4596999883651733</v>
       </c>
       <c r="H343">
         <v>0.5336999893188477</v>
@@ -12761,10 +12761,10 @@
         <v>2</v>
       </c>
       <c r="G345">
-        <v>0.2524000108242035</v>
+        <v>0.2524999976158142</v>
       </c>
       <c r="H345">
-        <v>0.7279999852180481</v>
+        <v>0.7279000282287598</v>
       </c>
     </row>
     <row r="346" spans="1:10">
@@ -12787,7 +12787,7 @@
         <v>0.4223999977111816</v>
       </c>
       <c r="J346">
-        <v>0.5698999762535095</v>
+        <v>0.5699999928474426</v>
       </c>
     </row>
     <row r="347" spans="1:10">
@@ -12899,10 +12899,10 @@
         <v>1</v>
       </c>
       <c r="G351">
-        <v>0.5914000272750854</v>
+        <v>0.5917999744415283</v>
       </c>
       <c r="J351">
-        <v>0.4007999897003174</v>
+        <v>0.4004999995231628</v>
       </c>
     </row>
     <row r="352" spans="1:10">
@@ -13065,10 +13065,10 @@
         <v>4</v>
       </c>
       <c r="I359">
-        <v>0.1816000044345856</v>
+        <v>0.1817000061273575</v>
       </c>
       <c r="J359">
-        <v>0.807699978351593</v>
+        <v>0.8076000213623047</v>
       </c>
     </row>
     <row r="360" spans="1:10">
@@ -13131,10 +13131,10 @@
         <v>3</v>
       </c>
       <c r="I362">
-        <v>0.6358000040054321</v>
+        <v>0.6359999775886536</v>
       </c>
       <c r="J362">
-        <v>0.3513999879360199</v>
+        <v>0.3512000143527985</v>
       </c>
     </row>
     <row r="363" spans="1:10">
@@ -13194,7 +13194,7 @@
         <v>4</v>
       </c>
       <c r="H365">
-        <v>0.4399000108242035</v>
+        <v>0.4399999976158142</v>
       </c>
       <c r="J365">
         <v>0.5455999970436096</v>
@@ -13515,10 +13515,10 @@
         <v>1</v>
       </c>
       <c r="G380">
-        <v>0.769599974155426</v>
+        <v>0.7695000171661377</v>
       </c>
       <c r="I380">
-        <v>0.2185000032186508</v>
+        <v>0.2186000049114227</v>
       </c>
     </row>
     <row r="381" spans="1:10">
@@ -13713,10 +13713,10 @@
         <v>2</v>
       </c>
       <c r="F389">
-        <v>0.1324999928474426</v>
+        <v>0.1324000060558319</v>
       </c>
       <c r="H389">
-        <v>0.8601999878883362</v>
+        <v>0.8603000044822693</v>
       </c>
     </row>
     <row r="390" spans="1:10">
@@ -13929,10 +13929,10 @@
         <v>3</v>
       </c>
       <c r="H398">
-        <v>0.246299996972084</v>
+        <v>0.2479999959468842</v>
       </c>
       <c r="I398">
-        <v>0.7372999787330627</v>
+        <v>0.7355999946594238</v>
       </c>
     </row>
     <row r="399" spans="1:10">
@@ -14012,10 +14012,10 @@
         <v>1</v>
       </c>
       <c r="G402">
-        <v>0.5609999895095825</v>
+        <v>0.5608999729156494</v>
       </c>
       <c r="H402">
-        <v>0.4368000030517578</v>
+        <v>0.4368999898433685</v>
       </c>
     </row>
     <row r="403" spans="1:10">
@@ -14207,10 +14207,10 @@
         <v>4</v>
       </c>
       <c r="H411">
-        <v>0.4415000081062317</v>
+        <v>0.4413999915122986</v>
       </c>
       <c r="J411">
-        <v>0.548799991607666</v>
+        <v>0.5489000082015991</v>
       </c>
     </row>
     <row r="412" spans="1:10">
@@ -14337,7 +14337,7 @@
         <v>0.4269999861717224</v>
       </c>
       <c r="J416">
-        <v>0.5665000081062317</v>
+        <v>0.5666000247001648</v>
       </c>
     </row>
     <row r="417" spans="1:10">
@@ -14724,7 +14724,7 @@
         <v>0.6370999813079834</v>
       </c>
       <c r="I434">
-        <v>0.3535999953746796</v>
+        <v>0.3535000085830688</v>
       </c>
     </row>
     <row r="435" spans="1:10">
@@ -14910,10 +14910,10 @@
         <v>3</v>
       </c>
       <c r="H443">
-        <v>0.3641000092029572</v>
+        <v>0.363999992609024</v>
       </c>
       <c r="I443">
-        <v>0.6243000030517578</v>
+        <v>0.6244000196456909</v>
       </c>
     </row>
     <row r="444" spans="1:10">
@@ -15131,7 +15131,7 @@
         <v>4</v>
       </c>
       <c r="I453">
-        <v>0.474700003862381</v>
+        <v>0.4747999906539917</v>
       </c>
       <c r="J453">
         <v>0.5181000232696533</v>
@@ -15300,7 +15300,7 @@
         <v>0.4850000143051147</v>
       </c>
       <c r="I461">
-        <v>0.504800021648407</v>
+        <v>0.5048999786376953</v>
       </c>
     </row>
     <row r="462" spans="1:10">
@@ -15506,7 +15506,7 @@
         <v>2</v>
       </c>
       <c r="G471">
-        <v>0.1993999928236008</v>
+        <v>0.1994999945163727</v>
       </c>
       <c r="H471">
         <v>0.7836999893188477</v>
@@ -15532,7 +15532,7 @@
         <v>0.6620000004768372</v>
       </c>
       <c r="J472">
-        <v>0.3287000060081482</v>
+        <v>0.3285999894142151</v>
       </c>
     </row>
     <row r="473" spans="1:10">
@@ -15802,7 +15802,7 @@
         <v>4</v>
       </c>
       <c r="G484">
-        <v>0.4469000101089478</v>
+        <v>0.4467999935150146</v>
       </c>
       <c r="J484">
         <v>0.5454000234603882</v>
@@ -16098,7 +16098,7 @@
         <v>0.4494999945163727</v>
       </c>
       <c r="I497">
-        <v>0.539900004863739</v>
+        <v>0.5400000214576721</v>
       </c>
     </row>
     <row r="498" spans="1:10">
@@ -16250,7 +16250,7 @@
         <v>4</v>
       </c>
       <c r="G504">
-        <v>0.1361999958753586</v>
+        <v>0.1360999941825867</v>
       </c>
       <c r="H504">
         <v>0.3770999908447266</v>
@@ -16356,10 +16356,10 @@
         <v>0</v>
       </c>
       <c r="F509">
-        <v>0.5486000180244446</v>
+        <v>0.5485000014305115</v>
       </c>
       <c r="I509">
-        <v>0.4314999878406525</v>
+        <v>0.4316000044345856</v>
       </c>
     </row>
     <row r="510" spans="1:10">
@@ -16617,10 +16617,10 @@
         <v>1</v>
       </c>
       <c r="G521">
-        <v>0.6284000277519226</v>
+        <v>0.6284999847412109</v>
       </c>
       <c r="H521">
-        <v>0.3546999990940094</v>
+        <v>0.3546000123023987</v>
       </c>
     </row>
     <row r="522" spans="1:10">
@@ -16726,13 +16726,13 @@
         <v>0.01070000045001507</v>
       </c>
       <c r="G526">
-        <v>0.393200010061264</v>
+        <v>0.3930999934673309</v>
       </c>
       <c r="H526">
         <v>0.01190000027418137</v>
       </c>
       <c r="I526">
-        <v>0.5751000046730042</v>
+        <v>0.5752000212669373</v>
       </c>
     </row>
     <row r="527" spans="1:10">
@@ -16752,10 +16752,10 @@
         <v>1</v>
       </c>
       <c r="G527">
-        <v>0.6969000101089478</v>
+        <v>0.6966999769210815</v>
       </c>
       <c r="I527">
-        <v>0.2867999970912933</v>
+        <v>0.2870000004768372</v>
       </c>
     </row>
     <row r="528" spans="1:10">
@@ -16775,10 +16775,10 @@
         <v>2</v>
       </c>
       <c r="F528">
-        <v>0.2308000028133392</v>
+        <v>0.2310999929904938</v>
       </c>
       <c r="H528">
-        <v>0.7537000179290771</v>
+        <v>0.7534999847412109</v>
       </c>
     </row>
     <row r="529" spans="1:10">
@@ -16904,7 +16904,7 @@
         <v>2</v>
       </c>
       <c r="G534">
-        <v>0.3264000117778778</v>
+        <v>0.3262999951839447</v>
       </c>
       <c r="H534">
         <v>0.6665999889373779</v>
@@ -17693,10 +17693,10 @@
         <v>2</v>
       </c>
       <c r="H570">
-        <v>0.4982999861240387</v>
+        <v>0.498199999332428</v>
       </c>
       <c r="J570">
-        <v>0.4968000054359436</v>
+        <v>0.4968999922275543</v>
       </c>
     </row>
     <row r="571" spans="1:10">
@@ -17788,10 +17788,10 @@
         <v>4</v>
       </c>
       <c r="G574">
-        <v>0.4839999973773956</v>
+        <v>0.4839000105857849</v>
       </c>
       <c r="J574">
-        <v>0.5059000253677368</v>
+        <v>0.5059999823570251</v>
       </c>
     </row>
     <row r="575" spans="1:10">
@@ -18228,10 +18228,10 @@
         <v>1</v>
       </c>
       <c r="F593">
-        <v>0.4945999979972839</v>
+        <v>0.494700014591217</v>
       </c>
       <c r="G593">
-        <v>0.4964999854564667</v>
+        <v>0.496399998664856</v>
       </c>
     </row>
     <row r="594" spans="1:10">
@@ -18458,7 +18458,7 @@
         <v>3</v>
       </c>
       <c r="I603">
-        <v>0.6155999898910522</v>
+        <v>0.6157000064849854</v>
       </c>
       <c r="J603">
         <v>0.3785000145435333</v>
@@ -18765,7 +18765,7 @@
         <v>0.122699998319149</v>
       </c>
       <c r="H617">
-        <v>0.8689000010490417</v>
+        <v>0.8687999844551086</v>
       </c>
     </row>
     <row r="618" spans="1:10">
@@ -18785,10 +18785,10 @@
         <v>4</v>
       </c>
       <c r="F618">
-        <v>0.3479999899864197</v>
+        <v>0.347900003194809</v>
       </c>
       <c r="J618">
-        <v>0.632099986076355</v>
+        <v>0.6322000026702881</v>
       </c>
     </row>
     <row r="619" spans="1:10">
@@ -19213,7 +19213,7 @@
         <v>4</v>
       </c>
       <c r="H637">
-        <v>0.3515999913215637</v>
+        <v>0.3517000079154968</v>
       </c>
       <c r="J637">
         <v>0.6255999803543091</v>
@@ -19279,7 +19279,7 @@
         <v>0</v>
       </c>
       <c r="F640">
-        <v>0.5144000053405762</v>
+        <v>0.5145000219345093</v>
       </c>
       <c r="I640">
         <v>0.4745000004768372</v>
@@ -19485,10 +19485,10 @@
         <v>2</v>
       </c>
       <c r="H650">
-        <v>0.741599977016449</v>
+        <v>0.7414000034332275</v>
       </c>
       <c r="I650">
-        <v>0.2454999983310699</v>
+        <v>0.2457000017166138</v>
       </c>
     </row>
     <row r="651" spans="1:10">
@@ -19528,10 +19528,10 @@
         <v>1</v>
       </c>
       <c r="G652">
-        <v>0.621999979019165</v>
+        <v>0.6215000152587891</v>
       </c>
       <c r="I652">
-        <v>0.3677999973297119</v>
+        <v>0.3682999908924103</v>
       </c>
     </row>
     <row r="653" spans="1:10">
@@ -19620,10 +19620,10 @@
         <v>0</v>
       </c>
       <c r="F656">
-        <v>0.7163000106811523</v>
+        <v>0.7164999842643738</v>
       </c>
       <c r="J656">
-        <v>0.2784000039100647</v>
+        <v>0.2782000005245209</v>
       </c>
     </row>
     <row r="657" spans="1:10">
@@ -19683,10 +19683,10 @@
         <v>2</v>
       </c>
       <c r="G659">
-        <v>0.4627000093460083</v>
+        <v>0.462799996137619</v>
       </c>
       <c r="H659">
-        <v>0.5327000021934509</v>
+        <v>0.5325999855995178</v>
       </c>
     </row>
     <row r="660" spans="1:10">
@@ -20127,7 +20127,7 @@
         <v>0.3136000037193298</v>
       </c>
       <c r="H680">
-        <v>0.4257000088691711</v>
+        <v>0.4257999956607819</v>
       </c>
       <c r="J680">
         <v>0.2560999989509583</v>
@@ -20346,13 +20346,13 @@
         <v>0</v>
       </c>
       <c r="F689">
-        <v>0.4025999903678894</v>
+        <v>0.4029000103473663</v>
       </c>
       <c r="H689">
-        <v>0.3373999893665314</v>
+        <v>0.3368000090122223</v>
       </c>
       <c r="I689">
-        <v>0.2558999955654144</v>
+        <v>0.2563000023365021</v>
       </c>
     </row>
     <row r="690" spans="1:10">
@@ -20518,7 +20518,7 @@
         <v>3</v>
       </c>
       <c r="I697">
-        <v>0.5189999938011169</v>
+        <v>0.5188999772071838</v>
       </c>
       <c r="J697">
         <v>0.4724999964237213</v>
@@ -20621,10 +20621,10 @@
         <v>2</v>
       </c>
       <c r="G702">
-        <v>0.3285999894142151</v>
+        <v>0.328000009059906</v>
       </c>
       <c r="H702">
-        <v>0.6582000255584717</v>
+        <v>0.6588000059127808</v>
       </c>
     </row>
     <row r="703" spans="1:10">
@@ -20644,10 +20644,10 @@
         <v>0</v>
       </c>
       <c r="F703">
-        <v>0.6840000152587891</v>
+        <v>0.683899998664856</v>
       </c>
       <c r="J703">
-        <v>0.3059000074863434</v>
+        <v>0.3059999942779541</v>
       </c>
     </row>
     <row r="704" spans="1:10">
@@ -20687,10 +20687,10 @@
         <v>3</v>
       </c>
       <c r="F705">
-        <v>0.3713000118732452</v>
+        <v>0.3711999952793121</v>
       </c>
       <c r="I705">
-        <v>0.616599977016449</v>
+        <v>0.6166999936103821</v>
       </c>
     </row>
     <row r="706" spans="1:10">
@@ -20963,7 +20963,7 @@
         <v>0</v>
       </c>
       <c r="F717">
-        <v>0.8777999877929688</v>
+        <v>0.8776999711990356</v>
       </c>
       <c r="I717">
         <v>0.1128999963402748</v>
@@ -21075,7 +21075,7 @@
         <v>0.3810999989509583</v>
       </c>
       <c r="G722">
-        <v>0.6014000177383423</v>
+        <v>0.6013000011444092</v>
       </c>
     </row>
     <row r="723" spans="1:10">
@@ -21121,10 +21121,10 @@
         <v>0.1272999942302704</v>
       </c>
       <c r="H724">
-        <v>0.4905000030994415</v>
+        <v>0.4905999898910522</v>
       </c>
       <c r="J724">
-        <v>0.3754000067710876</v>
+        <v>0.3752999901771545</v>
       </c>
     </row>
     <row r="725" spans="1:10">
@@ -21167,10 +21167,10 @@
         <v>3</v>
       </c>
       <c r="I726">
-        <v>0.7947999835014343</v>
+        <v>0.795199990272522</v>
       </c>
       <c r="J726">
-        <v>0.2010000050067902</v>
+        <v>0.2005999982357025</v>
       </c>
     </row>
     <row r="727" spans="1:10">
@@ -21342,10 +21342,10 @@
         <v>3</v>
       </c>
       <c r="H734">
-        <v>0.3837999999523163</v>
+        <v>0.3835000097751617</v>
       </c>
       <c r="I734">
-        <v>0.6093000173568726</v>
+        <v>0.6096000075340271</v>
       </c>
     </row>
     <row r="735" spans="1:10">
@@ -21431,10 +21431,10 @@
         <v>3</v>
       </c>
       <c r="F738">
-        <v>0.1659999936819077</v>
+        <v>0.1656000018119812</v>
       </c>
       <c r="I738">
-        <v>0.8205999732017517</v>
+        <v>0.820900022983551</v>
       </c>
     </row>
     <row r="739" spans="1:10">
@@ -21454,10 +21454,10 @@
         <v>3</v>
       </c>
       <c r="I739">
-        <v>0.6507999897003174</v>
+        <v>0.6506999731063843</v>
       </c>
       <c r="J739">
-        <v>0.3424000144004822</v>
+        <v>0.3425000011920929</v>
       </c>
     </row>
     <row r="740" spans="1:10">
@@ -21583,10 +21583,10 @@
         <v>0</v>
       </c>
       <c r="F745">
-        <v>0.5766000151634216</v>
+        <v>0.5764999985694885</v>
       </c>
       <c r="H745">
-        <v>0.4190999865531921</v>
+        <v>0.4192000031471252</v>
       </c>
     </row>
     <row r="746" spans="1:10">
@@ -21692,10 +21692,10 @@
         <v>2</v>
       </c>
       <c r="G750">
-        <v>0.3831999897956848</v>
+        <v>0.3844999969005585</v>
       </c>
       <c r="H750">
-        <v>0.603600025177002</v>
+        <v>0.6022999882698059</v>
       </c>
     </row>
     <row r="751" spans="1:10">
@@ -21747,7 +21747,7 @@
         <v>2</v>
       </c>
       <c r="H752">
-        <v>0.7199000120162964</v>
+        <v>0.7200000286102295</v>
       </c>
       <c r="J752">
         <v>0.2739000022411346</v>
@@ -21856,7 +21856,7 @@
         <v>4</v>
       </c>
       <c r="G757">
-        <v>0.2340999990701675</v>
+        <v>0.2342000007629395</v>
       </c>
       <c r="H757">
         <v>0.3429000079631805</v>
@@ -22046,10 +22046,10 @@
         <v>1</v>
       </c>
       <c r="G765">
-        <v>0.691100001335144</v>
+        <v>0.6912000179290771</v>
       </c>
       <c r="I765">
-        <v>0.3039999902248383</v>
+        <v>0.3039000034332275</v>
       </c>
     </row>
     <row r="766" spans="1:10">
@@ -22287,10 +22287,10 @@
         <v>2</v>
       </c>
       <c r="F776">
-        <v>0.3903000056743622</v>
+        <v>0.3889999985694885</v>
       </c>
       <c r="H776">
-        <v>0.5996999740600586</v>
+        <v>0.6010000109672546</v>
       </c>
     </row>
     <row r="777" spans="1:10">
@@ -22430,10 +22430,10 @@
         <v>0</v>
       </c>
       <c r="F783">
-        <v>0.8246999979019165</v>
+        <v>0.8248000144958496</v>
       </c>
       <c r="G783">
-        <v>0.1669999957084656</v>
+        <v>0.1668999940156937</v>
       </c>
     </row>
     <row r="784" spans="1:10">
@@ -22453,7 +22453,7 @@
         <v>2</v>
       </c>
       <c r="G784">
-        <v>0.2982999980449677</v>
+        <v>0.2982000112533569</v>
       </c>
       <c r="H784">
         <v>0.6985999941825867</v>
@@ -22476,7 +22476,7 @@
         <v>2</v>
       </c>
       <c r="H785">
-        <v>0.5206000208854675</v>
+        <v>0.5206999778747559</v>
       </c>
       <c r="J785">
         <v>0.4731999933719635</v>
@@ -22522,10 +22522,10 @@
         <v>1</v>
       </c>
       <c r="G787">
-        <v>0.6678000092506409</v>
+        <v>0.6682999730110168</v>
       </c>
       <c r="I787">
-        <v>0.3190999925136566</v>
+        <v>0.318699985742569</v>
       </c>
     </row>
     <row r="788" spans="1:10">
@@ -22565,10 +22565,10 @@
         <v>2</v>
       </c>
       <c r="F789">
-        <v>0.1928000003099442</v>
+        <v>0.1926999986171722</v>
       </c>
       <c r="H789">
-        <v>0.6190000176429749</v>
+        <v>0.6190999746322632</v>
       </c>
       <c r="I789">
         <v>0.1809999942779541</v>
@@ -22726,7 +22726,7 @@
         <v>1</v>
       </c>
       <c r="F796">
-        <v>0.1088000014424324</v>
+        <v>0.1086999997496605</v>
       </c>
       <c r="G796">
         <v>0.8823000192642212</v>
@@ -22749,7 +22749,7 @@
         <v>4</v>
       </c>
       <c r="G797">
-        <v>0.4679000079631805</v>
+        <v>0.4679999947547913</v>
       </c>
       <c r="J797">
         <v>0.5242999792098999</v>
@@ -22772,10 +22772,10 @@
         <v>4</v>
       </c>
       <c r="H798">
-        <v>0.4210000038146973</v>
+        <v>0.421099990606308</v>
       </c>
       <c r="J798">
-        <v>0.5673999786376953</v>
+        <v>0.567300021648407</v>
       </c>
     </row>
     <row r="799" spans="1:10">
@@ -22858,10 +22858,10 @@
         <v>4</v>
       </c>
       <c r="H802">
-        <v>0.3718999922275543</v>
+        <v>0.3718000054359436</v>
       </c>
       <c r="J802">
-        <v>0.6165000200271606</v>
+        <v>0.616599977016449</v>
       </c>
     </row>
     <row r="803" spans="1:10">
@@ -23067,7 +23067,7 @@
         <v>0</v>
       </c>
       <c r="F812">
-        <v>0.578499972820282</v>
+        <v>0.5784000158309937</v>
       </c>
       <c r="H812">
         <v>0.3086000084877014</v>
